--- a/cfg/excel/__tables__.xlsx
+++ b/cfg/excel/__tables__.xlsx
@@ -1,21 +1,38 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <TotalTime>0</TotalTime>
-  <Application>Go Excelize</Application>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowHeight="17655"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>xuri</dc:creator>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2006-09-16T00:00:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2006-09-16T00:00:00Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -74,13 +91,13 @@
     <t>output file name</t>
   </si>
   <si>
-    <t>item.TbItem</t>
+    <t>ItemCfg</t>
   </si>
   <si>
     <t>Item</t>
   </si>
   <si>
-    <t>item.xlsx</t>
+    <t>itemCfg.xlsx</t>
   </si>
   <si>
     <t>id</t>
@@ -92,63 +109,373 @@
     <t>item config table</t>
   </si>
   <si>
-    <t>weapon.TbWeapon</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>weapon.xlsx</t>
-  </si>
-  <si>
-    <t>weapon config table</t>
-  </si>
-  <si>
-    <t>bullet.TbBullet</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>bullet.xlsx</t>
-  </si>
-  <si>
-    <t>bullet config table</t>
-  </si>
-  <si>
-    <t>enemy.TbEnemy</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>enemy.xlsx</t>
-  </si>
-  <si>
-    <t>enemy config table</t>
+    <t>itemCfg</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -156,23 +483,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -214,7 +835,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -249,7 +870,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -423,30 +1044,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="122211"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <cols>
+    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="13.1428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -481,7 +1092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -516,11 +1127,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TbItem</t>
-        </is>
+    <row r="3" spans="1:11">
+      <c r="B3" t="s">
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -540,102 +1149,12 @@
       <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TbWeapon</t>
-        </is>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TbBullet</t>
-        </is>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TbEnemy</t>
-        </is>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
+      <c r="K3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/cfg/excel/__tables__.xlsx
+++ b/cfg/excel/__tables__.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -70,46 +71,271 @@
     <t>##</t>
   </si>
   <si>
-    <t>full name with module</t>
-  </si>
-  <si>
-    <t>record bean name</t>
-  </si>
-  <si>
-    <t>read schema from data file</t>
-  </si>
-  <si>
-    <t>input file list</t>
-  </si>
-  <si>
-    <t>index field</t>
-  </si>
-  <si>
-    <t>one|map|list</t>
-  </si>
-  <si>
-    <t>output file name</t>
+    <t>全名(包含模块和名字)</t>
+  </si>
+  <si>
+    <t>记录类名</t>
+  </si>
+  <si>
+    <t>从excel读取定义</t>
+  </si>
+  <si>
+    <t>文件列表</t>
+  </si>
+  <si>
+    <t>表id字段</t>
+  </si>
+  <si>
+    <t>模式</t>
+  </si>
+  <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>输出文件名</t>
+  </si>
+  <si>
+    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+  </si>
+  <si>
+    <t>可以多个，以逗号','分隔</t>
+  </si>
+  <si>
+    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+  </si>
+  <si>
+    <t>取值one|map|list，为空自动为map</t>
+  </si>
+  <si>
+    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+  </si>
+  <si>
+    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>EffectConfig</t>
+  </si>
+  <si>
+    <t>EffectCfg</t>
+  </si>
+  <si>
+    <t>EffectCfg.xlsx</t>
+  </si>
+  <si>
+    <t>LevelConfig</t>
+  </si>
+  <si>
+    <t>LevelCfg</t>
+  </si>
+  <si>
+    <t>LevelCfg/LevelCfg_1.xlsx,LevelCfg/LevelCfg_2.xlsx,LevelCfg/LevelCfg_3.xlsx</t>
+  </si>
+  <si>
+    <t>id+pointId</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>SceneConfig</t>
+  </si>
+  <si>
+    <t>SceneCfg</t>
+  </si>
+  <si>
+    <t>SceneCfg.xlsx</t>
+  </si>
+  <si>
+    <t>SkillTemplateConfig</t>
+  </si>
+  <si>
+    <t>SkillTemplateCfg</t>
+  </si>
+  <si>
+    <t>SkillTemplateCfg.xlsx</t>
+  </si>
+  <si>
+    <t>ItemConfig</t>
   </si>
   <si>
     <t>ItemCfg</t>
   </si>
   <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>itemCfg.xlsx</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>item config table</t>
-  </si>
-  <si>
-    <t>itemCfg</t>
+    <t>ItemCfg.xlsx</t>
+  </si>
+  <si>
+    <t>BuildingItemConfig</t>
+  </si>
+  <si>
+    <t>BuildingItemCfg</t>
+  </si>
+  <si>
+    <t>BuildingItemCfg.xlsx</t>
+  </si>
+  <si>
+    <t>MouseConfig</t>
+  </si>
+  <si>
+    <t>MouseCfg</t>
+  </si>
+  <si>
+    <t>MouseCfg.xlsx</t>
+  </si>
+  <si>
+    <t>LanguageConfig</t>
+  </si>
+  <si>
+    <t>LanguageCfg</t>
+  </si>
+  <si>
+    <t>LanguageCfg.xlsx</t>
+  </si>
+  <si>
+    <t>DialogueConfig</t>
+  </si>
+  <si>
+    <t>DialogueCfg</t>
+  </si>
+  <si>
+    <t>DialogueCfg.xlsx</t>
+  </si>
+  <si>
+    <t>CharacterConfig</t>
+  </si>
+  <si>
+    <t>CharacterCfg</t>
+  </si>
+  <si>
+    <t>CharacterCfg.xlsx</t>
+  </si>
+  <si>
+    <t>InputConfig</t>
+  </si>
+  <si>
+    <t>InputCfg</t>
+  </si>
+  <si>
+    <t>InputCfg.xlsx</t>
+  </si>
+  <si>
+    <t>GlobalConfig</t>
+  </si>
+  <si>
+    <t>GlobalCfg</t>
+  </si>
+  <si>
+    <t>GlobalCfg.xlsx</t>
+  </si>
+  <si>
+    <t>SkillConfig</t>
+  </si>
+  <si>
+    <t>SkillCfg</t>
+  </si>
+  <si>
+    <t>SkillCfg.xlsx</t>
+  </si>
+  <si>
+    <t>ActivityConfig</t>
+  </si>
+  <si>
+    <t>ActivityCfg</t>
+  </si>
+  <si>
+    <t>ActivityCfg.xlsx</t>
+  </si>
+  <si>
+    <t>FunctionConfig</t>
+  </si>
+  <si>
+    <t>FunctionCfg</t>
+  </si>
+  <si>
+    <t>FunctionCfg.xlsx</t>
+  </si>
+  <si>
+    <t>CollectionConfig</t>
+  </si>
+  <si>
+    <t>CollectionCfg</t>
+  </si>
+  <si>
+    <t>CollectionCfg.xlsx</t>
+  </si>
+  <si>
+    <t>RoleInfoConfig</t>
+  </si>
+  <si>
+    <t>RoleInfoCfg</t>
+  </si>
+  <si>
+    <t>RoleInfoCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeRoleConfig</t>
+  </si>
+  <si>
+    <t>AttributeRoleCfg</t>
+  </si>
+  <si>
+    <t>AttributeRole@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeWeaponConfig</t>
+  </si>
+  <si>
+    <t>AttributeWeaponCfg</t>
+  </si>
+  <si>
+    <t>AttributeWeapon@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeGearConfig</t>
+  </si>
+  <si>
+    <t>AttributeGearCfg</t>
+  </si>
+  <si>
+    <t>AttributeGear@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeSkillConfig</t>
+  </si>
+  <si>
+    <t>AttributeSkillCfg</t>
+  </si>
+  <si>
+    <t>AttributeSkill@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>WeaponConfig</t>
+  </si>
+  <si>
+    <t>WeaponCfg</t>
+  </si>
+  <si>
+    <t>WeaponCfg.xlsx</t>
+  </si>
+  <si>
+    <t>GearConfig</t>
+  </si>
+  <si>
+    <t>GearCfg</t>
+  </si>
+  <si>
+    <t>GearCfg.xlsx</t>
+  </si>
+  <si>
+    <t>DamageConfig</t>
+  </si>
+  <si>
+    <t>DamageCfg</t>
+  </si>
+  <si>
+    <t>DamageCfg.xlsx</t>
   </si>
 </sst>
 </file>
@@ -122,16 +348,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -247,13 +474,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -290,6 +510,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -309,12 +535,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,20 +803,22 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -605,7 +827,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -629,16 +851,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -647,90 +869,101 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -793,7 +1026,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -809,7 +1042,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -821,7 +1054,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -1050,110 +1283,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="13.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.575" customWidth="1"/>
+    <col min="4" max="4" width="32.425" customWidth="1"/>
+    <col min="5" max="5" width="72.875" customWidth="1"/>
+    <col min="6" max="6" width="22.375" customWidth="1"/>
+    <col min="7" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="B3" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:11">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:11">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:11">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:11">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:11">
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:11">
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:11">
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:11">
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:11">
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:11">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:11">
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:11">
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="20" customHeight="1" spans="1:11">
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="20" customHeight="1" spans="2:5">
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="20" customHeight="1" spans="2:5">
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="20" customHeight="1" spans="2:5">
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="2:5">
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="2:5">
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="20" customHeight="1" spans="2:5">
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="20" customHeight="1" spans="2:5">
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="2:5">
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="2:5">
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E21" r:id="rId1" display="AttributeRole@RoleAttributeCfg.xlsx"/>
+    <hyperlink ref="E22" r:id="rId2" display="AttributeWeapon@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeWeapon@RoleAttributeCfg.xlsx"/>
+    <hyperlink ref="E23" r:id="rId3" display="AttributeGear@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeGear@RoleAttributeCfg.xlsx"/>
+    <hyperlink ref="E24" r:id="rId4" display="AttributeSkill@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeSkill@RoleAttributeCfg.xlsx"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/cfg/excel/__tables__.xlsx
+++ b/cfg/excel/__tables__.xlsx
@@ -5,15 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\AppData\Local\Kingsoft\WPSOFF~1\1210~1.291\office6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Tables" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -92,70 +91,22 @@
     <t>分组</t>
   </si>
   <si>
-    <t>注释</t>
-  </si>
-  <si>
     <t>输出文件名</t>
   </si>
   <si>
     <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
   </si>
   <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+    <t>可以多个，以逗号分隔</t>
+  </si>
+  <si>
+    <t>为空自动取value_type中第一个字段</t>
   </si>
   <si>
     <t>取值one|map|list，为空自动为map</t>
   </si>
   <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>EffectConfig</t>
-  </si>
-  <si>
-    <t>EffectCfg</t>
-  </si>
-  <si>
-    <t>EffectCfg.xlsx</t>
-  </si>
-  <si>
-    <t>LevelConfig</t>
-  </si>
-  <si>
-    <t>LevelCfg</t>
-  </si>
-  <si>
-    <t>LevelCfg/LevelCfg_1.xlsx,LevelCfg/LevelCfg_2.xlsx,LevelCfg/LevelCfg_3.xlsx</t>
-  </si>
-  <si>
-    <t>id+pointId</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>SceneConfig</t>
-  </si>
-  <si>
-    <t>SceneCfg</t>
-  </si>
-  <si>
-    <t>SceneCfg.xlsx</t>
-  </si>
-  <si>
-    <t>SkillTemplateConfig</t>
-  </si>
-  <si>
-    <t>SkillTemplateCfg</t>
-  </si>
-  <si>
-    <t>SkillTemplateCfg.xlsx</t>
+    <t>取值c|s|e，空为所有分组</t>
   </si>
   <si>
     <t>ItemConfig</t>
@@ -167,175 +118,7 @@
     <t>ItemCfg.xlsx</t>
   </si>
   <si>
-    <t>BuildingItemConfig</t>
-  </si>
-  <si>
-    <t>BuildingItemCfg</t>
-  </si>
-  <si>
-    <t>BuildingItemCfg.xlsx</t>
-  </si>
-  <si>
-    <t>MouseConfig</t>
-  </si>
-  <si>
-    <t>MouseCfg</t>
-  </si>
-  <si>
-    <t>MouseCfg.xlsx</t>
-  </si>
-  <si>
-    <t>LanguageConfig</t>
-  </si>
-  <si>
-    <t>LanguageCfg</t>
-  </si>
-  <si>
-    <t>LanguageCfg.xlsx</t>
-  </si>
-  <si>
-    <t>DialogueConfig</t>
-  </si>
-  <si>
-    <t>DialogueCfg</t>
-  </si>
-  <si>
-    <t>DialogueCfg.xlsx</t>
-  </si>
-  <si>
-    <t>CharacterConfig</t>
-  </si>
-  <si>
-    <t>CharacterCfg</t>
-  </si>
-  <si>
-    <t>CharacterCfg.xlsx</t>
-  </si>
-  <si>
-    <t>InputConfig</t>
-  </si>
-  <si>
-    <t>InputCfg</t>
-  </si>
-  <si>
-    <t>InputCfg.xlsx</t>
-  </si>
-  <si>
-    <t>GlobalConfig</t>
-  </si>
-  <si>
-    <t>GlobalCfg</t>
-  </si>
-  <si>
-    <t>GlobalCfg.xlsx</t>
-  </si>
-  <si>
-    <t>SkillConfig</t>
-  </si>
-  <si>
-    <t>SkillCfg</t>
-  </si>
-  <si>
-    <t>SkillCfg.xlsx</t>
-  </si>
-  <si>
-    <t>ActivityConfig</t>
-  </si>
-  <si>
-    <t>ActivityCfg</t>
-  </si>
-  <si>
-    <t>ActivityCfg.xlsx</t>
-  </si>
-  <si>
-    <t>FunctionConfig</t>
-  </si>
-  <si>
-    <t>FunctionCfg</t>
-  </si>
-  <si>
-    <t>FunctionCfg.xlsx</t>
-  </si>
-  <si>
-    <t>CollectionConfig</t>
-  </si>
-  <si>
-    <t>CollectionCfg</t>
-  </si>
-  <si>
-    <t>CollectionCfg.xlsx</t>
-  </si>
-  <si>
-    <t>RoleInfoConfig</t>
-  </si>
-  <si>
-    <t>RoleInfoCfg</t>
-  </si>
-  <si>
-    <t>RoleInfoCfg.xlsx</t>
-  </si>
-  <si>
-    <t>AttributeRoleConfig</t>
-  </si>
-  <si>
-    <t>AttributeRoleCfg</t>
-  </si>
-  <si>
-    <t>AttributeRole@RoleAttributeCfg.xlsx</t>
-  </si>
-  <si>
-    <t>AttributeWeaponConfig</t>
-  </si>
-  <si>
-    <t>AttributeWeaponCfg</t>
-  </si>
-  <si>
-    <t>AttributeWeapon@RoleAttributeCfg.xlsx</t>
-  </si>
-  <si>
-    <t>AttributeGearConfig</t>
-  </si>
-  <si>
-    <t>AttributeGearCfg</t>
-  </si>
-  <si>
-    <t>AttributeGear@RoleAttributeCfg.xlsx</t>
-  </si>
-  <si>
-    <t>AttributeSkillConfig</t>
-  </si>
-  <si>
-    <t>AttributeSkillCfg</t>
-  </si>
-  <si>
-    <t>AttributeSkill@RoleAttributeCfg.xlsx</t>
-  </si>
-  <si>
-    <t>WeaponConfig</t>
-  </si>
-  <si>
-    <t>WeaponCfg</t>
-  </si>
-  <si>
-    <t>WeaponCfg.xlsx</t>
-  </si>
-  <si>
-    <t>GearConfig</t>
-  </si>
-  <si>
-    <t>GearCfg</t>
-  </si>
-  <si>
-    <t>GearCfg.xlsx</t>
-  </si>
-  <si>
-    <t>DamageConfig</t>
-  </si>
-  <si>
-    <t>DamageCfg</t>
-  </si>
-  <si>
-    <t>DamageCfg.xlsx</t>
+    <t>id</t>
   </si>
 </sst>
 </file>
@@ -352,22 +135,15 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -375,14 +151,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -390,7 +166,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -398,7 +174,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -406,7 +182,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -414,7 +190,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -422,14 +198,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -437,7 +213,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -445,7 +221,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -453,14 +229,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -468,35 +244,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -510,31 +293,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,55 +604,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -951,17 +734,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,7 +790,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1026,9 +1014,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1042,40 +1030,40 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1108,9 +1096,9 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1138,66 +1126,40 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1211,20 +1173,38 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1283,469 +1263,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.575" customWidth="1"/>
-    <col min="4" max="4" width="32.425" customWidth="1"/>
-    <col min="5" max="5" width="72.875" customWidth="1"/>
-    <col min="6" max="6" width="22.375" customWidth="1"/>
-    <col min="7" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="23.75" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
+    <row r="4" spans="1:11">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="C4" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:11">
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:11">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:11">
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:11">
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:11">
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:11">
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:11">
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:11">
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:11">
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:11">
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:11">
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:11">
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="20" customHeight="1" spans="1:11">
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" ht="20" customHeight="1" spans="2:5">
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" ht="20" customHeight="1" spans="2:5">
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" ht="20" customHeight="1" spans="2:5">
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="2:5">
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="2:5">
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" ht="20" customHeight="1" spans="2:5">
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" ht="20" customHeight="1" spans="2:5">
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="2:5">
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="2:5">
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>100</v>
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E21" r:id="rId1" display="AttributeRole@RoleAttributeCfg.xlsx"/>
-    <hyperlink ref="E22" r:id="rId2" display="AttributeWeapon@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeWeapon@RoleAttributeCfg.xlsx"/>
-    <hyperlink ref="E23" r:id="rId3" display="AttributeGear@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeGear@RoleAttributeCfg.xlsx"/>
-    <hyperlink ref="E24" r:id="rId4" display="AttributeSkill@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeSkill@RoleAttributeCfg.xlsx"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/cfg/excel/__tables__.xlsx
+++ b/cfg/excel/__tables__.xlsx
@@ -5,14 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\AppData\Local\Kingsoft\WPSOFF~1\1210~1.291\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="16995"/>
   </bookViews>
   <sheets>
-    <sheet name="Tables" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -91,22 +92,70 @@
     <t>分组</t>
   </si>
   <si>
+    <t>注释</t>
+  </si>
+  <si>
     <t>输出文件名</t>
   </si>
   <si>
     <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
   </si>
   <si>
-    <t>可以多个，以逗号分隔</t>
-  </si>
-  <si>
-    <t>为空自动取value_type中第一个字段</t>
+    <t>可以多个，以逗号','分隔</t>
+  </si>
+  <si>
+    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
   </si>
   <si>
     <t>取值one|map|list，为空自动为map</t>
   </si>
   <si>
-    <t>取值c|s|e，空为所有分组</t>
+    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+  </si>
+  <si>
+    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>EffectConfig</t>
+  </si>
+  <si>
+    <t>EffectCfg</t>
+  </si>
+  <si>
+    <t>EffectCfg.xlsx</t>
+  </si>
+  <si>
+    <t>LevelConfig</t>
+  </si>
+  <si>
+    <t>LevelCfg</t>
+  </si>
+  <si>
+    <t>LevelCfg/LevelCfg_1.xlsx,LevelCfg/LevelCfg_2.xlsx,LevelCfg/LevelCfg_3.xlsx</t>
+  </si>
+  <si>
+    <t>id+pointId</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>SceneConfig</t>
+  </si>
+  <si>
+    <t>SceneCfg</t>
+  </si>
+  <si>
+    <t>SceneCfg.xlsx</t>
+  </si>
+  <si>
+    <t>SkillTemplateConfig</t>
+  </si>
+  <si>
+    <t>SkillTemplateCfg</t>
+  </si>
+  <si>
+    <t>SkillTemplateCfg.xlsx</t>
   </si>
   <si>
     <t>ItemConfig</t>
@@ -118,7 +167,178 @@
     <t>ItemCfg.xlsx</t>
   </si>
   <si>
-    <t>id</t>
+    <t>BuildingItemConfig</t>
+  </si>
+  <si>
+    <t>BuildingItemCfg</t>
+  </si>
+  <si>
+    <t>BuildingItemCfg.xlsx</t>
+  </si>
+  <si>
+    <t>MouseConfig</t>
+  </si>
+  <si>
+    <t>MouseCfg</t>
+  </si>
+  <si>
+    <t>MouseCfg.xlsx</t>
+  </si>
+  <si>
+    <t>LanguageConfig</t>
+  </si>
+  <si>
+    <t>LanguageCfg</t>
+  </si>
+  <si>
+    <t>LanguageCfg.xlsx</t>
+  </si>
+  <si>
+    <t>DialogueConfig</t>
+  </si>
+  <si>
+    <t>DialogueCfg</t>
+  </si>
+  <si>
+    <t>DialogueCfg.xlsx</t>
+  </si>
+  <si>
+    <t>CharacterConfig</t>
+  </si>
+  <si>
+    <t>CharacterCfg</t>
+  </si>
+  <si>
+    <t>CharacterCfg.xlsx</t>
+  </si>
+  <si>
+    <t>InputConfig</t>
+  </si>
+  <si>
+    <t>InputCfg</t>
+  </si>
+  <si>
+    <t>InputCfg.xlsx</t>
+  </si>
+  <si>
+    <t>GlobalConfig</t>
+  </si>
+  <si>
+    <t>GlobalCfg</t>
+  </si>
+  <si>
+    <t>GlobalCfg.xlsx</t>
+  </si>
+  <si>
+    <t>SkillConfig</t>
+  </si>
+  <si>
+    <t>SkillCfg</t>
+  </si>
+  <si>
+    <t>SkillCfg.xlsx</t>
+  </si>
+  <si>
+    <t>ActivityConfig</t>
+  </si>
+  <si>
+    <t>ActivityCfg</t>
+  </si>
+  <si>
+    <t>ActivityCfg.xlsx</t>
+  </si>
+  <si>
+    <t>FunctionConfig</t>
+  </si>
+  <si>
+    <t>FunctionCfg</t>
+  </si>
+  <si>
+    <t>FunctionCfg.xlsx</t>
+  </si>
+  <si>
+    <t>CollectionConfig</t>
+  </si>
+  <si>
+    <t>CollectionCfg</t>
+  </si>
+  <si>
+    <t>CollectionCfg.xlsx</t>
+  </si>
+  <si>
+    <t>RoleInfoConfig</t>
+  </si>
+  <si>
+    <t>RoleInfoCfg</t>
+  </si>
+  <si>
+    <t>RoleInfoCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeRoleConfig</t>
+  </si>
+  <si>
+    <t>AttributeRoleCfg</t>
+  </si>
+  <si>
+    <t>AttributeRole@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeWeaponConfig</t>
+  </si>
+  <si>
+    <t>AttributeWeaponCfg</t>
+  </si>
+  <si>
+    <t>AttributeWeapon@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeGearConfig</t>
+  </si>
+  <si>
+    <t>AttributeGearCfg</t>
+  </si>
+  <si>
+    <t>AttributeGear@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>AttributeSkillConfig</t>
+  </si>
+  <si>
+    <t>AttributeSkillCfg</t>
+  </si>
+  <si>
+    <t>AttributeSkill@RoleAttributeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>WeaponConfig</t>
+  </si>
+  <si>
+    <t>WeaponCfg</t>
+  </si>
+  <si>
+    <t>WeaponCfg.xlsx</t>
+  </si>
+  <si>
+    <t>GearConfig</t>
+  </si>
+  <si>
+    <t>GearCfg</t>
+  </si>
+  <si>
+    <t>GearCfg.xlsx</t>
+  </si>
+  <si>
+    <t>DamageConfig</t>
+  </si>
+  <si>
+    <t>DamageCfg</t>
+  </si>
+  <si>
+    <t>DamageCfg.xlsx</t>
+  </si>
+  <si>
+    <t>id+level</t>
   </si>
 </sst>
 </file>
@@ -135,7 +355,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -143,7 +370,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -151,14 +378,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -166,7 +393,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +401,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -182,7 +409,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -190,7 +417,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,14 +425,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -213,7 +440,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -221,7 +448,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -229,14 +456,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -244,42 +471,35 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -293,6 +513,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -312,12 +538,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,55 +824,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -734,8 +954,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,221 +1019,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1014,9 +1029,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1030,40 +1045,40 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1096,9 +1111,9 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1126,40 +1141,66 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1173,38 +1214,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1263,111 +1286,475 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.575" customWidth="1"/>
+    <col min="4" max="4" width="32.425" customWidth="1"/>
+    <col min="5" max="5" width="72.875" customWidth="1"/>
+    <col min="6" max="6" width="22.375" customWidth="1"/>
+    <col min="7" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="23.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:11">
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:11">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:11">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:11">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:11">
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:11">
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:11">
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:11">
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:11">
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:11">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:11">
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:11">
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="20" customHeight="1" spans="1:11">
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="20" customHeight="1" spans="2:7">
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="20" customHeight="1" spans="2:7">
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="20" customHeight="1" spans="2:7">
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="2:7">
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="2:7">
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="20" customHeight="1" spans="2:7">
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="20" customHeight="1" spans="2:7">
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="2:7">
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="2:7">
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E21" r:id="rId1" display="AttributeRole@RoleAttributeCfg.xlsx"/>
+    <hyperlink ref="E22" r:id="rId2" display="AttributeWeapon@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeWeapon@RoleAttributeCfg.xlsx"/>
+    <hyperlink ref="E23" r:id="rId3" display="AttributeGear@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeGear@RoleAttributeCfg.xlsx"/>
+    <hyperlink ref="E24" r:id="rId4" display="AttributeSkill@RoleAttributeCfg.xlsx" tooltip="mailto:AttributeSkill@RoleAttributeCfg.xlsx"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/cfg/excel/__tables__.xlsx
+++ b/cfg/excel/__tables__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16995"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>##var</t>
   </si>
@@ -320,13 +320,13 @@
     <t>WeaponCfg.xlsx</t>
   </si>
   <si>
-    <t>GearConfig</t>
-  </si>
-  <si>
-    <t>GearCfg</t>
-  </si>
-  <si>
-    <t>GearCfg.xlsx</t>
+    <t>EquipConfig</t>
+  </si>
+  <si>
+    <t>EquipCfg</t>
+  </si>
+  <si>
+    <t>EquipCfg.xlsx</t>
   </si>
   <si>
     <t>DamageConfig</t>
@@ -339,6 +339,33 @@
   </si>
   <si>
     <t>id+level</t>
+  </si>
+  <si>
+    <t>RechargeConfig</t>
+  </si>
+  <si>
+    <t>RechargeCfg</t>
+  </si>
+  <si>
+    <t>RechargeCfg.xlsx</t>
+  </si>
+  <si>
+    <t>GiftConfig</t>
+  </si>
+  <si>
+    <t>GiftCfg</t>
+  </si>
+  <si>
+    <t>GiftCfg.xlsx</t>
+  </si>
+  <si>
+    <t>ExchangeConfig</t>
+  </si>
+  <si>
+    <t>ExchangeCfg</t>
+  </si>
+  <si>
+    <t>ExchangeCfg.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1313,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
@@ -1734,6 +1761,48 @@
       </c>
       <c r="G27" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
